--- a/artfynd/A 50866-2024 artfynd.xlsx
+++ b/artfynd/A 50866-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149565</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50866-2024 artfynd.xlsx
+++ b/artfynd/A 50866-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149565</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50866-2024 artfynd.xlsx
+++ b/artfynd/A 50866-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149565</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
